--- a/Bases_de_Dados/FootyStats/Saudi Arabia Professional League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Saudi Arabia Professional League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP213"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.17</v>
@@ -3748,7 +3748,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR15" t="n">
         <v>0.91</v>
@@ -4620,7 +4620,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5271,10 +5271,10 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ23" t="n">
         <v>1</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.83</v>
@@ -6143,7 +6143,7 @@
         <v>3</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.5</v>
@@ -6800,7 +6800,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR29" t="n">
         <v>1.46</v>
@@ -7018,7 +7018,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR30" t="n">
         <v>1.47</v>
@@ -7236,7 +7236,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR31" t="n">
         <v>2.32</v>
@@ -7890,7 +7890,7 @@
         <v>2</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR34" t="n">
         <v>1.79</v>
@@ -8323,7 +8323,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.83</v>
@@ -8759,7 +8759,7 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.5</v>
@@ -10503,7 +10503,7 @@
         <v>2</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ46" t="n">
         <v>2.27</v>
@@ -10724,7 +10724,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR47" t="n">
         <v>0.87</v>
@@ -10939,10 +10939,10 @@
         <v>3</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR48" t="n">
         <v>0.83</v>
@@ -11157,7 +11157,7 @@
         <v>2</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ49" t="n">
         <v>2.42</v>
@@ -11593,7 +11593,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ51" t="n">
         <v>1</v>
@@ -12029,10 +12029,10 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR53" t="n">
         <v>1.65</v>
@@ -12468,7 +12468,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ55" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR55" t="n">
         <v>1</v>
@@ -15081,10 +15081,10 @@
         <v>0.75</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR67" t="n">
         <v>1.62</v>
@@ -15299,10 +15299,10 @@
         <v>0.33</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR68" t="n">
         <v>0.86</v>
@@ -15520,7 +15520,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR69" t="n">
         <v>1.61</v>
@@ -15735,7 +15735,7 @@
         <v>2.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ70" t="n">
         <v>2.33</v>
@@ -15953,10 +15953,10 @@
         <v>3</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ71" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR71" t="n">
         <v>1.5</v>
@@ -18569,7 +18569,7 @@
         <v>1.6</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.17</v>
@@ -18787,7 +18787,7 @@
         <v>0.2</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.17</v>
@@ -19444,7 +19444,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR87" t="n">
         <v>1.35</v>
@@ -19877,7 +19877,7 @@
         <v>0.5</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.67</v>
@@ -20098,7 +20098,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR90" t="n">
         <v>2.55</v>
@@ -21406,7 +21406,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ96" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR96" t="n">
         <v>0.86</v>
@@ -21839,7 +21839,7 @@
         <v>2</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.5</v>
@@ -22493,7 +22493,7 @@
         <v>1.17</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ101" t="n">
         <v>1</v>
@@ -22714,7 +22714,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR102" t="n">
         <v>0.84</v>
@@ -22932,7 +22932,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ103" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR103" t="n">
         <v>1.56</v>
@@ -23365,10 +23365,10 @@
         <v>0.6</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR105" t="n">
         <v>1.04</v>
@@ -23586,7 +23586,7 @@
         <v>2</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR106" t="n">
         <v>1.65</v>
@@ -24019,7 +24019,7 @@
         <v>0.2</v>
       </c>
       <c r="AP108" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ108" t="n">
         <v>0.5</v>
@@ -24891,7 +24891,7 @@
         <v>1.4</v>
       </c>
       <c r="AP112" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.33</v>
@@ -25763,7 +25763,7 @@
         <v>0.83</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.91</v>
@@ -26856,7 +26856,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ121" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR121" t="n">
         <v>2.17</v>
@@ -27074,7 +27074,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR122" t="n">
         <v>1.14</v>
@@ -27725,7 +27725,7 @@
         <v>1</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.83</v>
@@ -27946,7 +27946,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR126" t="n">
         <v>1.58</v>
@@ -28379,7 +28379,7 @@
         <v>1.14</v>
       </c>
       <c r="AP128" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ128" t="n">
         <v>0.91</v>
@@ -28600,7 +28600,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR129" t="n">
         <v>1.5</v>
@@ -29033,7 +29033,7 @@
         <v>0.86</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.67</v>
@@ -29908,7 +29908,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR135" t="n">
         <v>1.4</v>
@@ -30123,7 +30123,7 @@
         <v>2.67</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ136" t="n">
         <v>2.33</v>
@@ -30562,7 +30562,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR138" t="n">
         <v>1.51</v>
@@ -31434,7 +31434,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ142" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR142" t="n">
         <v>1.12</v>
@@ -32085,7 +32085,7 @@
         <v>2.14</v>
       </c>
       <c r="AP145" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ145" t="n">
         <v>1.5</v>
@@ -32739,7 +32739,7 @@
         <v>2.29</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ148" t="n">
         <v>2.42</v>
@@ -32957,7 +32957,7 @@
         <v>2</v>
       </c>
       <c r="AP149" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ149" t="n">
         <v>2.27</v>
@@ -33175,7 +33175,7 @@
         <v>1.13</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.91</v>
@@ -33832,7 +33832,7 @@
         <v>2</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR153" t="n">
         <v>1.77</v>
@@ -34050,7 +34050,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR154" t="n">
         <v>2.22</v>
@@ -34265,7 +34265,7 @@
         <v>0.25</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.5</v>
@@ -34701,7 +34701,7 @@
         <v>1.22</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ157" t="n">
         <v>1</v>
@@ -35355,7 +35355,7 @@
         <v>2.5</v>
       </c>
       <c r="AP160" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ160" t="n">
         <v>2.33</v>
@@ -35576,7 +35576,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR161" t="n">
         <v>1.24</v>
@@ -35794,7 +35794,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ162" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR162" t="n">
         <v>1.18</v>
@@ -36009,7 +36009,7 @@
         <v>0.78</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ163" t="n">
         <v>0.67</v>
@@ -36884,7 +36884,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ167" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR167" t="n">
         <v>1.4</v>
@@ -37538,7 +37538,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR170" t="n">
         <v>1.1</v>
@@ -37974,7 +37974,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR172" t="n">
         <v>1</v>
@@ -38189,7 +38189,7 @@
         <v>0.2</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ173" t="n">
         <v>0.17</v>
@@ -38843,7 +38843,7 @@
         <v>0.33</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.5</v>
@@ -39933,7 +39933,7 @@
         <v>1</v>
       </c>
       <c r="AP181" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ181" t="n">
         <v>0.91</v>
@@ -40154,7 +40154,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR182" t="n">
         <v>1.16</v>
@@ -40369,7 +40369,7 @@
         <v>1.67</v>
       </c>
       <c r="AP183" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.58</v>
@@ -40590,7 +40590,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ184" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR184" t="n">
         <v>1.26</v>
@@ -41677,10 +41677,10 @@
         <v>1.11</v>
       </c>
       <c r="AP189" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR189" t="n">
         <v>1.24</v>
@@ -41898,7 +41898,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ190" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR190" t="n">
         <v>1.52</v>
@@ -44296,7 +44296,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AR201" t="n">
         <v>1.49</v>
@@ -44511,7 +44511,7 @@
         <v>1.6</v>
       </c>
       <c r="AP202" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.33</v>
@@ -45168,7 +45168,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR205" t="n">
         <v>1.33</v>
@@ -45601,10 +45601,10 @@
         <v>2.27</v>
       </c>
       <c r="AP207" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AQ207" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AR207" t="n">
         <v>1.22</v>
@@ -45819,7 +45819,7 @@
         <v>1.64</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ208" t="n">
         <v>1.58</v>
@@ -46988,6 +46988,878 @@
       </c>
       <c r="BP213" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>8197954</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>46081.66666666666</v>
+      </c>
+      <c r="F214" t="n">
+        <v>24</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" t="n">
+        <v>2</v>
+      </c>
+      <c r="K214" t="n">
+        <v>3</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="n">
+        <v>2</v>
+      </c>
+      <c r="N214" t="n">
+        <v>3</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>['4', '39']</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R214" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S214" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U214" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V214" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W214" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X214" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>8197940</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>46081.66666666666</v>
+      </c>
+      <c r="F215" t="n">
+        <v>24</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Al Quadisiya</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Al Taawon</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" t="n">
+        <v>2</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>1</v>
+      </c>
+      <c r="N215" t="n">
+        <v>2</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>['45+4']</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R215" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="S215" t="n">
+        <v>6</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U215" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V215" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X215" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB215" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BE215" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BI215" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM215" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BN215" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO215" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BP215" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>8198122</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>46081.66666666666</v>
+      </c>
+      <c r="F216" t="n">
+        <v>24</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Al Akhdoud</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>1</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" t="n">
+        <v>2</v>
+      </c>
+      <c r="L216" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" t="n">
+        <v>3</v>
+      </c>
+      <c r="N216" t="n">
+        <v>4</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>['14', '64', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R216" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S216" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U216" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V216" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W216" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X216" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV216" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA216" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB216" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BE216" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF216" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI216" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ216" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BK216" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM216" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN216" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO216" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP216" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>8198121</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>46081.66666666666</v>
+      </c>
+      <c r="F217" t="n">
+        <v>24</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Al Feiha</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>1</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>1</v>
+      </c>
+      <c r="L217" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" t="n">
+        <v>3</v>
+      </c>
+      <c r="N217" t="n">
+        <v>4</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>['72', '80', '85']</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R217" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S217" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U217" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="V217" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X217" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AU217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB217" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC217" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE217" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF217" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI217" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ217" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK217" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL217" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM217" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BN217" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO217" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP217" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Saudi Arabia Professional League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Saudi Arabia Professional League_20252026.xlsx
@@ -46706,13 +46706,13 @@
         <v>2.55</v>
       </c>
       <c r="AU212" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV212" t="n">
         <v>3</v>
       </c>
       <c r="AW212" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX212" t="n">
         <v>5</v>
@@ -47366,13 +47366,13 @@
         <v>1</v>
       </c>
       <c r="AW215" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX215" t="n">
         <v>1</v>
       </c>
       <c r="AY215" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ215" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Saudi Arabia Professional League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Saudi Arabia Professional League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.17</v>
@@ -1568,7 +1568,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.58</v>
@@ -6582,7 +6582,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR28" t="n">
         <v>3.18</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.33</v>
@@ -10070,7 +10070,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR44" t="n">
         <v>1.46</v>
@@ -12683,7 +12683,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.91</v>
@@ -12904,7 +12904,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR57" t="n">
         <v>1.73</v>
@@ -16828,7 +16828,7 @@
         <v>2</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR75" t="n">
         <v>1.43</v>
@@ -17261,7 +17261,7 @@
         <v>0</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.17</v>
@@ -24022,7 +24022,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR108" t="n">
         <v>1.81</v>
@@ -24237,7 +24237,7 @@
         <v>2.6</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ109" t="n">
         <v>2.33</v>
@@ -27289,7 +27289,7 @@
         <v>2.33</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.5</v>
@@ -27510,7 +27510,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR124" t="n">
         <v>1.55</v>
@@ -30998,7 +30998,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR140" t="n">
         <v>1.13</v>
@@ -31431,7 +31431,7 @@
         <v>1.86</v>
       </c>
       <c r="AP142" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ142" t="n">
         <v>2.38</v>
@@ -34268,7 +34268,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR155" t="n">
         <v>1.19</v>
@@ -37535,7 +37535,7 @@
         <v>1.13</v>
       </c>
       <c r="AP170" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.33</v>
@@ -38846,7 +38846,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR176" t="n">
         <v>1.36</v>
@@ -40151,7 +40151,7 @@
         <v>1.8</v>
       </c>
       <c r="AP182" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ182" t="n">
         <v>1.58</v>
@@ -42334,7 +42334,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ192" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR192" t="n">
         <v>1.07</v>
@@ -43203,7 +43203,7 @@
         <v>0.64</v>
       </c>
       <c r="AP196" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ196" t="n">
         <v>0.83</v>
@@ -44075,7 +44075,7 @@
         <v>2.3</v>
       </c>
       <c r="AP200" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AQ200" t="n">
         <v>2.42</v>
@@ -44732,7 +44732,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ203" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR203" t="n">
         <v>1.64</v>
@@ -47860,6 +47860,224 @@
       </c>
       <c r="BP217" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>8197968</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>46086.66666666666</v>
+      </c>
+      <c r="F218" t="n">
+        <v>25</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Al Riyadh</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>1</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>1</v>
+      </c>
+      <c r="L218" t="n">
+        <v>3</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="n">
+        <v>3</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>['35', '53', '60']</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R218" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S218" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="T218" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U218" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V218" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="W218" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X218" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU218" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX218" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY218" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ218" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA218" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB218" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC218" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE218" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI218" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ218" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BK218" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM218" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BN218" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO218" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP218" t="n">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Saudi Arabia Professional League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Saudi Arabia Professional League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP218"/>
+  <dimension ref="A1:BP222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.58</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.46</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ7" t="n">
         <v>2.38</v>
@@ -2440,7 +2440,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR12" t="n">
         <v>1.49</v>
@@ -3312,7 +3312,7 @@
         <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.83</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ16" t="n">
         <v>2.27</v>
@@ -4184,7 +4184,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.33</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ25" t="n">
         <v>2.33</v>
@@ -6146,7 +6146,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR26" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR27" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.58</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.33</v>
@@ -8762,7 +8762,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR38" t="n">
         <v>0.79</v>
@@ -8980,7 +8980,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AR39" t="n">
         <v>1.11</v>
@@ -9195,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="AP40" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.83</v>
@@ -9634,7 +9634,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR42" t="n">
         <v>0.89</v>
@@ -9852,7 +9852,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR43" t="n">
         <v>2.73</v>
@@ -10067,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.46</v>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.67</v>
@@ -12686,7 +12686,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR56" t="n">
         <v>1.16</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.46</v>
@@ -13340,7 +13340,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AR59" t="n">
         <v>0.89</v>
@@ -13555,7 +13555,7 @@
         <v>1</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.83</v>
@@ -13776,7 +13776,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR61" t="n">
         <v>0.66</v>
@@ -13991,7 +13991,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ62" t="n">
         <v>2.27</v>
@@ -14209,10 +14209,10 @@
         <v>2.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR63" t="n">
         <v>1.6</v>
@@ -16610,7 +16610,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR74" t="n">
         <v>1.24</v>
@@ -17043,7 +17043,7 @@
         <v>1.75</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ76" t="n">
         <v>2.27</v>
@@ -17264,7 +17264,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AR77" t="n">
         <v>1.13</v>
@@ -17697,10 +17697,10 @@
         <v>0.5</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR79" t="n">
         <v>2.16</v>
@@ -18351,7 +18351,7 @@
         <v>2.25</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.58</v>
@@ -18572,7 +18572,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR83" t="n">
         <v>1.04</v>
@@ -18790,7 +18790,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AR84" t="n">
         <v>1.34</v>
@@ -19659,7 +19659,7 @@
         <v>1.4</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ88" t="n">
         <v>1</v>
@@ -20531,10 +20531,10 @@
         <v>0.4</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR92" t="n">
         <v>1.46</v>
@@ -20752,7 +20752,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR93" t="n">
         <v>1.06</v>
@@ -20967,10 +20967,10 @@
         <v>0.17</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AR94" t="n">
         <v>1.14</v>
@@ -21185,7 +21185,7 @@
         <v>1.2</v>
       </c>
       <c r="AP95" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.83</v>
@@ -21842,7 +21842,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR98" t="n">
         <v>1.35</v>
@@ -22929,7 +22929,7 @@
         <v>2.6</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ103" t="n">
         <v>2.38</v>
@@ -24455,10 +24455,10 @@
         <v>1.71</v>
       </c>
       <c r="AP110" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR110" t="n">
         <v>2.21</v>
@@ -25109,7 +25109,7 @@
         <v>1</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.67</v>
@@ -25327,7 +25327,7 @@
         <v>0.5</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.83</v>
@@ -25548,7 +25548,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR115" t="n">
         <v>1.32</v>
@@ -25766,7 +25766,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR116" t="n">
         <v>1.36</v>
@@ -26420,7 +26420,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AR119" t="n">
         <v>1.16</v>
@@ -26853,7 +26853,7 @@
         <v>2.17</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ121" t="n">
         <v>2.38</v>
@@ -27292,7 +27292,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR123" t="n">
         <v>1.15</v>
@@ -27943,7 +27943,7 @@
         <v>2.5</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.58</v>
@@ -28382,7 +28382,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR128" t="n">
         <v>1.09</v>
@@ -28597,7 +28597,7 @@
         <v>0.17</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.33</v>
@@ -30344,7 +30344,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AR137" t="n">
         <v>1.73</v>
@@ -30777,7 +30777,7 @@
         <v>1.38</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ139" t="n">
         <v>1</v>
@@ -31649,10 +31649,10 @@
         <v>1.5</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR143" t="n">
         <v>1.3</v>
@@ -31867,7 +31867,7 @@
         <v>0.88</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.83</v>
@@ -32088,7 +32088,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR145" t="n">
         <v>1.81</v>
@@ -32303,7 +32303,7 @@
         <v>0.38</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.83</v>
@@ -33178,7 +33178,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR150" t="n">
         <v>1.1</v>
@@ -34483,7 +34483,7 @@
         <v>2</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.33</v>
@@ -34922,7 +34922,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR158" t="n">
         <v>1.57</v>
@@ -35573,7 +35573,7 @@
         <v>0.13</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.33</v>
@@ -36448,7 +36448,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR165" t="n">
         <v>1.53</v>
@@ -36666,7 +36666,7 @@
         <v>2</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AR166" t="n">
         <v>1.85</v>
@@ -37099,7 +37099,7 @@
         <v>2.38</v>
       </c>
       <c r="AP168" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ168" t="n">
         <v>2.42</v>
@@ -37753,7 +37753,7 @@
         <v>2.11</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ171" t="n">
         <v>2.27</v>
@@ -38192,7 +38192,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ173" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AR173" t="n">
         <v>1.12</v>
@@ -38625,10 +38625,10 @@
         <v>1.4</v>
       </c>
       <c r="AP175" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR175" t="n">
         <v>1.63</v>
@@ -39282,7 +39282,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR178" t="n">
         <v>2.24</v>
@@ -39715,7 +39715,7 @@
         <v>1.1</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ180" t="n">
         <v>1</v>
@@ -39936,7 +39936,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR181" t="n">
         <v>1.61</v>
@@ -41023,7 +41023,7 @@
         <v>1.78</v>
       </c>
       <c r="AP186" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.33</v>
@@ -42116,7 +42116,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ191" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR191" t="n">
         <v>1.06</v>
@@ -42549,10 +42549,10 @@
         <v>0.18</v>
       </c>
       <c r="AP193" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AR193" t="n">
         <v>1.67</v>
@@ -42985,7 +42985,7 @@
         <v>0.64</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.83</v>
@@ -43421,7 +43421,7 @@
         <v>1.5</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ197" t="n">
         <v>1.58</v>
@@ -43639,10 +43639,10 @@
         <v>1.6</v>
       </c>
       <c r="AP198" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR198" t="n">
         <v>1.86</v>
@@ -43860,7 +43860,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR199" t="n">
         <v>2.2</v>
@@ -44950,7 +44950,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR204" t="n">
         <v>1.38</v>
@@ -45165,7 +45165,7 @@
         <v>1</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ205" t="n">
         <v>1.33</v>
@@ -45383,7 +45383,7 @@
         <v>2.4</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ206" t="n">
         <v>2.33</v>
@@ -48078,6 +48078,878 @@
       </c>
       <c r="BP218" t="n">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>8197927</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F219" t="n">
+        <v>25</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Al Hazm</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>2</v>
+      </c>
+      <c r="M219" t="n">
+        <v>1</v>
+      </c>
+      <c r="N219" t="n">
+        <v>3</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>['60', '72']</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R219" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S219" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T219" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U219" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V219" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W219" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X219" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT219" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU219" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV219" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW219" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX219" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY219" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ219" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA219" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB219" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC219" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE219" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF219" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG219" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH219" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI219" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ219" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK219" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL219" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM219" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN219" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO219" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP219" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>8198109</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F220" t="n">
+        <v>25</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>1</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>1</v>
+      </c>
+      <c r="L220" t="n">
+        <v>3</v>
+      </c>
+      <c r="M220" t="n">
+        <v>1</v>
+      </c>
+      <c r="N220" t="n">
+        <v>4</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>['23', '59', '84']</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R220" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S220" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U220" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V220" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W220" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X220" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM220" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN220" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO220" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP220" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>8197990</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F221" t="n">
+        <v>25</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Al Taawon</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Al Fateh</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>1</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" t="n">
+        <v>3</v>
+      </c>
+      <c r="M221" t="n">
+        <v>2</v>
+      </c>
+      <c r="N221" t="n">
+        <v>5</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>['45+4', '59', '63']</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>['68', '90']</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R221" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S221" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T221" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U221" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="V221" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W221" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X221" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO221" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP221" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>8197879</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F222" t="n">
+        <v>25</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>1</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>1</v>
+      </c>
+      <c r="L222" t="n">
+        <v>4</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>4</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>['43', '81', '84', '86']</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R222" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="S222" t="n">
+        <v>10</v>
+      </c>
+      <c r="T222" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="U222" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V222" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W222" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X222" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT222" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU222" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW222" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY222" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ222" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA222" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB222" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC222" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BE222" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF222" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG222" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH222" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI222" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ222" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK222" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL222" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM222" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN222" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO222" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP222" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Saudi Arabia Professional League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Saudi Arabia Professional League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP222"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.33</v>
@@ -1350,7 +1350,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.38</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ11" t="n">
         <v>2.42</v>
@@ -3530,7 +3530,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ15" t="n">
         <v>1.58</v>
@@ -3966,7 +3966,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR16" t="n">
         <v>1.8</v>
@@ -4402,7 +4402,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR18" t="n">
         <v>0.97</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.33</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.67</v>
@@ -5710,7 +5710,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.46</v>
@@ -8108,7 +8108,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR35" t="n">
         <v>0.87</v>
@@ -8326,7 +8326,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR36" t="n">
         <v>1.3</v>
@@ -8544,7 +8544,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR37" t="n">
         <v>1.62</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.15</v>
@@ -9198,7 +9198,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR40" t="n">
         <v>1.78</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ41" t="n">
         <v>2.33</v>
@@ -9631,7 +9631,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.08</v>
@@ -9849,7 +9849,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.83</v>
@@ -10506,7 +10506,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR46" t="n">
         <v>1.47</v>
@@ -13119,10 +13119,10 @@
         <v>2</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR58" t="n">
         <v>1.35</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.15</v>
@@ -13558,7 +13558,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR60" t="n">
         <v>2.42</v>
@@ -13773,7 +13773,7 @@
         <v>1.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.08</v>
@@ -13994,7 +13994,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ62" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR62" t="n">
         <v>1.23</v>
@@ -14427,10 +14427,10 @@
         <v>2</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR64" t="n">
         <v>2.78</v>
@@ -16607,7 +16607,7 @@
         <v>1.25</v>
       </c>
       <c r="AP74" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.08</v>
@@ -17046,7 +17046,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ76" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR76" t="n">
         <v>1.85</v>
@@ -17479,10 +17479,10 @@
         <v>1.5</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR78" t="n">
         <v>0.83</v>
@@ -17915,10 +17915,10 @@
         <v>0.67</v>
       </c>
       <c r="AP80" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR80" t="n">
         <v>1.4</v>
@@ -18133,7 +18133,7 @@
         <v>1.75</v>
       </c>
       <c r="AP81" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ81" t="n">
         <v>1</v>
@@ -18354,7 +18354,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR82" t="n">
         <v>1.2</v>
@@ -19441,7 +19441,7 @@
         <v>3</v>
       </c>
       <c r="AP87" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.58</v>
@@ -20095,7 +20095,7 @@
         <v>0.25</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.33</v>
@@ -20316,7 +20316,7 @@
         <v>2</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR91" t="n">
         <v>1.52</v>
@@ -21188,7 +21188,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR95" t="n">
         <v>1.66</v>
@@ -21403,7 +21403,7 @@
         <v>3</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ96" t="n">
         <v>2.38</v>
@@ -21621,7 +21621,7 @@
         <v>0.6</v>
       </c>
       <c r="AP97" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.67</v>
@@ -22060,7 +22060,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR99" t="n">
         <v>1.63</v>
@@ -22275,7 +22275,7 @@
         <v>2.5</v>
       </c>
       <c r="AP100" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ100" t="n">
         <v>2.33</v>
@@ -22711,7 +22711,7 @@
         <v>0.2</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.33</v>
@@ -23150,7 +23150,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR104" t="n">
         <v>1.58</v>
@@ -23804,7 +23804,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR107" t="n">
         <v>1.13</v>
@@ -24673,10 +24673,10 @@
         <v>1.67</v>
       </c>
       <c r="AP111" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ111" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR111" t="n">
         <v>2.41</v>
@@ -25330,7 +25330,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR114" t="n">
         <v>1.19</v>
@@ -25545,7 +25545,7 @@
         <v>2.2</v>
       </c>
       <c r="AP115" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.38</v>
@@ -25984,7 +25984,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR117" t="n">
         <v>1.3</v>
@@ -26199,7 +26199,7 @@
         <v>2</v>
       </c>
       <c r="AP118" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ118" t="n">
         <v>2.42</v>
@@ -26635,7 +26635,7 @@
         <v>1.14</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ120" t="n">
         <v>1</v>
@@ -27071,7 +27071,7 @@
         <v>1</v>
       </c>
       <c r="AP122" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.33</v>
@@ -27728,7 +27728,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR125" t="n">
         <v>1.81</v>
@@ -28164,7 +28164,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR127" t="n">
         <v>1.66</v>
@@ -29251,7 +29251,7 @@
         <v>2.17</v>
       </c>
       <c r="AP132" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ132" t="n">
         <v>2.42</v>
@@ -29469,10 +29469,10 @@
         <v>0.43</v>
       </c>
       <c r="AP133" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR133" t="n">
         <v>2.3</v>
@@ -29690,7 +29690,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ134" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR134" t="n">
         <v>1.39</v>
@@ -30995,7 +30995,7 @@
         <v>0.14</v>
       </c>
       <c r="AP140" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ140" t="n">
         <v>0.46</v>
@@ -31213,10 +31213,10 @@
         <v>1.86</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR141" t="n">
         <v>1.01</v>
@@ -31870,7 +31870,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR144" t="n">
         <v>2.01</v>
@@ -32306,7 +32306,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR146" t="n">
         <v>1.57</v>
@@ -32521,7 +32521,7 @@
         <v>1.86</v>
       </c>
       <c r="AP147" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.33</v>
@@ -32960,7 +32960,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ149" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR149" t="n">
         <v>1.21</v>
@@ -34047,7 +34047,7 @@
         <v>2.25</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.58</v>
@@ -35140,7 +35140,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR159" t="n">
         <v>1.36</v>
@@ -35791,7 +35791,7 @@
         <v>2</v>
       </c>
       <c r="AP162" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ162" t="n">
         <v>2.38</v>
@@ -36230,7 +36230,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR164" t="n">
         <v>1.81</v>
@@ -37317,10 +37317,10 @@
         <v>1.75</v>
       </c>
       <c r="AP169" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR169" t="n">
         <v>1.11</v>
@@ -37756,7 +37756,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ171" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR171" t="n">
         <v>1.48</v>
@@ -37971,7 +37971,7 @@
         <v>2</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.58</v>
@@ -38407,7 +38407,7 @@
         <v>2.33</v>
       </c>
       <c r="AP174" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ174" t="n">
         <v>2.33</v>
@@ -39061,7 +39061,7 @@
         <v>0.7</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ177" t="n">
         <v>0.67</v>
@@ -39279,7 +39279,7 @@
         <v>1.78</v>
       </c>
       <c r="AP178" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.38</v>
@@ -39497,10 +39497,10 @@
         <v>0.7</v>
       </c>
       <c r="AP179" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR179" t="n">
         <v>1.11</v>
@@ -40372,7 +40372,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR183" t="n">
         <v>1.67</v>
@@ -41244,7 +41244,7 @@
         <v>2</v>
       </c>
       <c r="AQ187" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR187" t="n">
         <v>1.82</v>
@@ -42113,7 +42113,7 @@
         <v>1</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ191" t="n">
         <v>0.83</v>
@@ -42331,7 +42331,7 @@
         <v>0.3</v>
       </c>
       <c r="AP192" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ192" t="n">
         <v>0.46</v>
@@ -42767,10 +42767,10 @@
         <v>2.2</v>
       </c>
       <c r="AP194" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ194" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AR194" t="n">
         <v>1.07</v>
@@ -42988,7 +42988,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR195" t="n">
         <v>1.36</v>
@@ -43206,7 +43206,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ196" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR196" t="n">
         <v>1.16</v>
@@ -43424,7 +43424,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR197" t="n">
         <v>1.43</v>
@@ -43857,7 +43857,7 @@
         <v>1.27</v>
       </c>
       <c r="AP199" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.08</v>
@@ -45822,7 +45822,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR208" t="n">
         <v>1.15</v>
@@ -48950,6 +48950,878 @@
       </c>
       <c r="BP222" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>8198056</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>46088.66666666666</v>
+      </c>
+      <c r="F223" t="n">
+        <v>25</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Al Quadisiya</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>1</v>
+      </c>
+      <c r="J223" t="n">
+        <v>3</v>
+      </c>
+      <c r="K223" t="n">
+        <v>4</v>
+      </c>
+      <c r="L223" t="n">
+        <v>1</v>
+      </c>
+      <c r="M223" t="n">
+        <v>4</v>
+      </c>
+      <c r="N223" t="n">
+        <v>5</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>['2', '21', '27', '74']</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="R223" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="S223" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T223" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U223" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V223" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W223" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X223" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV223" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW223" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX223" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY223" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ223" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA223" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB223" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC223" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD223" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE223" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BF223" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BG223" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH223" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI223" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ223" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK223" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL223" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM223" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BN223" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO223" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP223" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>8198123</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>46088.66666666666</v>
+      </c>
+      <c r="F224" t="n">
+        <v>25</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>1</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>1</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R224" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="S224" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="T224" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U224" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="V224" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W224" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X224" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AN224" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT224" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU224" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW224" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX224" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY224" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA224" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB224" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC224" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD224" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BE224" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF224" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BG224" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH224" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI224" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ224" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK224" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL224" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM224" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN224" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO224" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP224" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="n">
+        <v>8197982</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>46088.66666666666</v>
+      </c>
+      <c r="F225" t="n">
+        <v>25</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Al Akhdoud</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Al Feiha</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>1</v>
+      </c>
+      <c r="K225" t="n">
+        <v>1</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
+        <v>5</v>
+      </c>
+      <c r="N225" t="n">
+        <v>5</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>['11', '55', '61', '66', '90+1']</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="R225" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S225" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T225" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U225" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V225" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W225" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X225" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH225" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI225" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN225" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR225" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS225" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT225" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AU225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV225" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW225" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX225" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY225" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ225" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA225" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB225" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC225" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD225" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BE225" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF225" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BG225" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH225" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI225" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BJ225" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BK225" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BL225" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BM225" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN225" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO225" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP225" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>8197983</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>46088.66666666666</v>
+      </c>
+      <c r="F226" t="n">
+        <v>25</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Al Ittifaq</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Al Shabab</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>1</v>
+      </c>
+      <c r="M226" t="n">
+        <v>1</v>
+      </c>
+      <c r="N226" t="n">
+        <v>2</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R226" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S226" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T226" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U226" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V226" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="W226" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X226" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AK226" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM226" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN226" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO226" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ226" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT226" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU226" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV226" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW226" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX226" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY226" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ226" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA226" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB226" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC226" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD226" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BE226" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF226" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BG226" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH226" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BI226" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ226" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK226" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BL226" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM226" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN226" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO226" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BP226" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>
